--- a/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
+++ b/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T11:15:53+00:00</t>
+    <t>2026-05-08T09:03:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
+++ b/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2443" uniqueCount="507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2444" uniqueCount="508">
   <si>
     <t>Property</t>
   </si>
@@ -51,16 +51,19 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T09:03:17+00:00</t>
+    <t>2026-05-08T09:31:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>GCS score/profile generated from build_observation_glasgow_coma_scale().</t>
+    <t>Specialized functional score profile for Glasgow Coma Scale values captured by the registry.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -118,9 +121,6 @@
   </si>
   <si>
     <t>Abstract</t>
-  </si>
-  <si>
-    <t>false</t>
   </si>
   <si>
     <t>Derivation</t>
@@ -741,7 +741,7 @@
     <t>Observation.status</t>
   </si>
   <si>
-    <t>registered | preliminary | final | amended +</t>
+    <t>Final registry observation</t>
   </si>
   <si>
     <t>The status of the result value.</t>
@@ -815,7 +815,7 @@
 </t>
   </si>
   <si>
-    <t>Type of observation (code / type)</t>
+    <t>Functional or severity score instrument</t>
   </si>
   <si>
     <t>Describes what was observed. Sometimes this is called the observation "name".</t>
@@ -859,10 +859,10 @@
 </t>
   </si>
   <si>
-    <t>Who and/or what the observation is about</t>
-  </si>
-  <si>
-    <t>The patient, or group of patients, location, device, organization, procedure or practitioner this observation is about and into whose or what record the observation is placed. If the actual focus of the observation is different from the subject (or a sample of, part, or region of the subject), the `focus` element or the `code` itself specifies the actual focus of the observation.</t>
+    <t>RES-Q registry patient</t>
+  </si>
+  <si>
+    <t>Patient who experienced the index stroke episode represented in this registry dataset.</t>
   </si>
   <si>
     <t>One would expect this element to be a cardinality of 1..1. The only circumstance in which the subject can be missing is when the observation is made by a device that does not know the patient. In this case, the observation SHALL be matched to a patient through some context/channel matching technique, and at this point, the observation should be updated. The subject of an Observation may in some cases be a procedure.  This supports the regulatory inspection use case where observations are captured during inspections of a procedure that is being performed (independent of any particular patient or whether patient related at all).</t>
@@ -913,10 +913,10 @@
 </t>
   </si>
   <si>
-    <t>Healthcare event during which this observation is made</t>
-  </si>
-  <si>
-    <t>The healthcare event  (e.g. a patient and healthcare provider interaction) during which this observation is made.</t>
+    <t>Index stroke encounter</t>
+  </si>
+  <si>
+    <t>Encounter that anchors the clinical fact to the acute stroke episode and hospital pathway.</t>
   </si>
   <si>
     <t>This will typically be the encounter the event occurred within, but some events may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter (e.g. pre-admission laboratory tests).</t>
@@ -1032,7 +1032,7 @@
 integer</t>
   </si>
   <si>
-    <t>Actual result</t>
+    <t>Recorded score value</t>
   </si>
   <si>
     <t>The information determined as a result of making the observation, if the information has a simple value.</t>
@@ -1079,6 +1079,9 @@
   </si>
   <si>
     <t>valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>Actual result</t>
   </si>
   <si>
     <t>http://tecnomod-um.org/ValueSet/gcsscore-vs</t>
@@ -1833,98 +1836,100 @@
       <c r="A7" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
@@ -2118,10 +2123,10 @@
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
@@ -2203,7 +2208,7 @@
         <v>82</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG2" t="s" s="2">
         <v>80</v>
@@ -5865,7 +5870,7 @@
         <v>243</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="M33" t="s" s="2">
         <v>324</v>
@@ -5903,7 +5908,7 @@
       </c>
       <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>82</v>
@@ -5956,10 +5961,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5985,16 +5990,16 @@
         <v>243</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -6022,10 +6027,10 @@
         <v>258</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>82</v>
@@ -6043,7 +6048,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6052,7 +6057,7 @@
         <v>94</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>106</v>
@@ -6070,7 +6075,7 @@
         <v>139</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>82</v>
@@ -6078,14 +6083,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6107,16 +6112,16 @@
         <v>243</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -6144,10 +6149,10 @@
         <v>258</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>82</v>
@@ -6165,7 +6170,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6186,24 +6191,24 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6226,19 +6231,19 @@
         <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6287,7 +6292,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6311,10 +6316,10 @@
         <v>82</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>82</v>
@@ -6322,10 +6327,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6351,13 +6356,13 @@
         <v>243</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6383,13 +6388,13 @@
         <v>82</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>82</v>
@@ -6407,7 +6412,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6416,7 +6421,7 @@
         <v>94</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>106</v>
@@ -6428,24 +6433,24 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6468,16 +6473,16 @@
         <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6527,7 +6532,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6536,7 +6541,7 @@
         <v>94</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>106</v>
@@ -6554,7 +6559,7 @@
         <v>82</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>82</v>
@@ -6562,10 +6567,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6591,16 +6596,16 @@
         <v>243</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6625,13 +6630,13 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -6649,7 +6654,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6673,10 +6678,10 @@
         <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>82</v>
@@ -6684,10 +6689,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6710,16 +6715,16 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6769,7 +6774,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6781,7 +6786,7 @@
         <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>82</v>
@@ -6790,24 +6795,24 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6830,16 +6835,16 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6889,7 +6894,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6910,24 +6915,24 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6953,16 +6958,16 @@
         <v>186</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -7011,7 +7016,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7023,7 +7028,7 @@
         <v>82</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>82</v>
@@ -7035,10 +7040,10 @@
         <v>82</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>82</v>
@@ -7046,10 +7051,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7164,10 +7169,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7284,10 +7289,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7406,10 +7411,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7432,13 +7437,13 @@
         <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7489,7 +7494,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7498,7 +7503,7 @@
         <v>94</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>106</v>
@@ -7513,10 +7518,10 @@
         <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>82</v>
@@ -7524,10 +7529,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7550,13 +7555,13 @@
         <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7607,7 +7612,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7616,7 +7621,7 @@
         <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>106</v>
@@ -7631,10 +7636,10 @@
         <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>82</v>
@@ -7642,10 +7647,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7671,10 +7676,10 @@
         <v>243</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7704,10 +7709,10 @@
         <v>258</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -7725,7 +7730,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7749,10 +7754,10 @@
         <v>82</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>82</v>
@@ -7760,10 +7765,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7789,16 +7794,16 @@
         <v>243</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -7826,10 +7831,10 @@
         <v>248</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -7847,7 +7852,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7868,13 +7873,13 @@
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>82</v>
@@ -7882,10 +7887,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7911,16 +7916,16 @@
         <v>243</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -7945,13 +7950,13 @@
         <v>82</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>82</v>
@@ -7969,7 +7974,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7990,13 +7995,13 @@
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>82</v>
@@ -8004,10 +8009,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8030,17 +8035,17 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8089,7 +8094,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8116,7 +8121,7 @@
         <v>82</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>82</v>
@@ -8124,10 +8129,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8150,13 +8155,13 @@
         <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8207,7 +8212,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8216,7 +8221,7 @@
         <v>94</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>106</v>
@@ -8231,10 +8236,10 @@
         <v>82</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>82</v>
@@ -8242,10 +8247,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8268,16 +8273,16 @@
         <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8327,7 +8332,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8351,7 +8356,7 @@
         <v>82</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>209</v>
@@ -8362,10 +8367,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8388,16 +8393,16 @@
         <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8447,7 +8452,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8471,10 +8476,10 @@
         <v>82</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>82</v>
@@ -8482,10 +8487,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8511,16 +8516,16 @@
         <v>186</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -8569,7 +8574,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8593,10 +8598,10 @@
         <v>82</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>82</v>
@@ -8604,10 +8609,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8722,10 +8727,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8842,10 +8847,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8964,10 +8969,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8993,13 +8998,13 @@
         <v>243</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="O59" t="s" s="2">
         <v>257</v>
@@ -9027,13 +9032,13 @@
         <v>82</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>82</v>
@@ -9051,7 +9056,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>94</v>
@@ -9072,7 +9077,7 @@
         <v>262</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>264</v>
@@ -9086,10 +9091,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9112,16 +9117,16 @@
         <v>95</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="M60" t="s" s="2">
         <v>324</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O60" t="s" s="2">
         <v>326</v>
@@ -9173,7 +9178,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9194,7 +9199,7 @@
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>331</v>
@@ -9208,10 +9213,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9237,16 +9242,16 @@
         <v>243</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9274,10 +9279,10 @@
         <v>258</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9295,7 +9300,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9322,7 +9327,7 @@
         <v>139</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>82</v>
@@ -9330,14 +9335,14 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9359,16 +9364,16 @@
         <v>243</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>82</v>
@@ -9396,10 +9401,10 @@
         <v>258</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>82</v>
@@ -9417,7 +9422,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9438,24 +9443,24 @@
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9481,16 +9486,16 @@
         <v>83</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
@@ -9539,7 +9544,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9563,10 +9568,10 @@
         <v>82</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>82</v>

--- a/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
+++ b/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T09:31:23+00:00</t>
+    <t>2026-05-08T10:13:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
+++ b/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2444" uniqueCount="508">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2443" uniqueCount="509">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T10:13:17+00:00</t>
+    <t>2026-05-11T15:54:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1084,7 +1084,7 @@
     <t>Actual result</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/ValueSet/gcsscore-vs</t>
+    <t>http://tecnomod-um.org/ValueSet/mrs-score-vs</t>
   </si>
   <si>
     <t>Observation.dataAbsentReason</t>
@@ -1135,10 +1135,7 @@
     <t>For some results, particularly numeric results, an interpretation is necessary to fully understand the significance of a result.</t>
   </si>
   <si>
-    <t>Codes identifying interpretations of observations.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|5.0.0</t>
+    <t>http://tecnomod-um.org/ValueSet/gcsscore-vs</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1620,6 +1617,12 @@
   </si>
   <si>
     <t>Observation.component.interpretation</t>
+  </si>
+  <si>
+    <t>Codes identifying interpretations of observations.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|5.0.0</t>
   </si>
   <si>
     <t>Observation.component.referenceRange</t>
@@ -6148,11 +6151,9 @@
       <c r="X35" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="Y35" t="s" s="2">
+      <c r="Y35" s="2"/>
+      <c r="Z35" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="Z35" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>82</v>
@@ -6191,24 +6192,24 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="AN35" t="s" s="2">
+      <c r="AO35" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AO35" t="s" s="2">
+      <c r="AP35" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="AP35" t="s" s="2">
-        <v>358</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6231,19 +6232,19 @@
         <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="N36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6292,7 +6293,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6316,10 +6317,10 @@
         <v>82</v>
       </c>
       <c r="AN36" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="AO36" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="AO36" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>82</v>
@@ -6327,10 +6328,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6356,13 +6357,13 @@
         <v>243</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6388,14 +6389,14 @@
         <v>82</v>
       </c>
       <c r="X37" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="Y37" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="Y37" t="s" s="2">
+      <c r="Z37" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="Z37" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AA37" t="s" s="2">
         <v>82</v>
       </c>
@@ -6412,7 +6413,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6421,7 +6422,7 @@
         <v>94</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>106</v>
@@ -6433,24 +6434,24 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="AN37" t="s" s="2">
+      <c r="AO37" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="AO37" t="s" s="2">
+      <c r="AP37" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="AP37" t="s" s="2">
-        <v>378</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6473,16 +6474,16 @@
         <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6532,7 +6533,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6541,7 +6542,7 @@
         <v>94</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>106</v>
@@ -6559,7 +6560,7 @@
         <v>82</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>82</v>
@@ -6567,10 +6568,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6596,16 +6597,16 @@
         <v>243</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>388</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6630,14 +6631,14 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="Y39" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="Z39" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="Z39" t="s" s="2">
-        <v>390</v>
-      </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
       </c>
@@ -6654,7 +6655,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6678,10 +6679,10 @@
         <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AO39" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>82</v>
@@ -6689,10 +6690,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6715,16 +6716,16 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6774,7 +6775,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6786,33 +6787,33 @@
         <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM40" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="AK40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM40" t="s" s="2">
+      <c r="AN40" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="AN40" t="s" s="2">
+      <c r="AO40" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="AO40" t="s" s="2">
+      <c r="AP40" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="AP40" t="s" s="2">
-        <v>402</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6835,16 +6836,16 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6894,7 +6895,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6915,24 +6916,24 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AN41" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="AN41" t="s" s="2">
+      <c r="AO41" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="AO41" t="s" s="2">
+      <c r="AP41" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="AP41" t="s" s="2">
-        <v>411</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6958,16 +6959,16 @@
         <v>186</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="N42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -7016,7 +7017,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7028,22 +7029,22 @@
         <v>82</v>
       </c>
       <c r="AJ42" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="AK42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN42" t="s" s="2">
+      <c r="AO42" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>82</v>
@@ -7051,10 +7052,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7169,10 +7170,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7289,10 +7290,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7411,10 +7412,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7437,13 +7438,13 @@
         <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7494,7 +7495,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7503,7 +7504,7 @@
         <v>94</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>106</v>
@@ -7518,10 +7519,10 @@
         <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>82</v>
@@ -7529,10 +7530,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7555,13 +7556,13 @@
         <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7612,7 +7613,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7621,7 +7622,7 @@
         <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>106</v>
@@ -7636,10 +7637,10 @@
         <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>82</v>
@@ -7647,10 +7648,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7676,10 +7677,10 @@
         <v>243</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7709,11 +7710,11 @@
         <v>258</v>
       </c>
       <c r="Y48" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="Z48" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="Z48" t="s" s="2">
-        <v>437</v>
-      </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
       </c>
@@ -7730,7 +7731,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7754,10 +7755,10 @@
         <v>82</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>82</v>
@@ -7765,10 +7766,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7794,16 +7795,16 @@
         <v>243</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="N49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -7831,11 +7832,11 @@
         <v>248</v>
       </c>
       <c r="Y49" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="Z49" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="Z49" t="s" s="2">
-        <v>445</v>
-      </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
       </c>
@@ -7852,7 +7853,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7873,13 +7874,13 @@
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="AN49" t="s" s="2">
-        <v>447</v>
-      </c>
       <c r="AO49" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>82</v>
@@ -7887,10 +7888,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7916,16 +7917,16 @@
         <v>243</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="N50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -7950,14 +7951,14 @@
         <v>82</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="Y50" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="Z50" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="Z50" t="s" s="2">
-        <v>454</v>
-      </c>
       <c r="AA50" t="s" s="2">
         <v>82</v>
       </c>
@@ -7974,7 +7975,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7995,13 +7996,13 @@
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AN50" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="AN50" t="s" s="2">
-        <v>447</v>
-      </c>
       <c r="AO50" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>82</v>
@@ -8009,10 +8010,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8035,17 +8036,17 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8094,7 +8095,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8121,7 +8122,7 @@
         <v>82</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>82</v>
@@ -8129,10 +8130,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8155,13 +8156,13 @@
         <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8212,7 +8213,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8221,7 +8222,7 @@
         <v>94</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>106</v>
@@ -8236,10 +8237,10 @@
         <v>82</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>82</v>
@@ -8247,10 +8248,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8273,16 +8274,16 @@
         <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>470</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8332,7 +8333,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8356,7 +8357,7 @@
         <v>82</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>209</v>
@@ -8367,10 +8368,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8393,16 +8394,16 @@
         <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>474</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>476</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8452,7 +8453,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8476,10 +8477,10 @@
         <v>82</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>82</v>
@@ -8487,10 +8488,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8516,16 +8517,16 @@
         <v>186</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="N55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>482</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -8574,7 +8575,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8598,10 +8599,10 @@
         <v>82</v>
       </c>
       <c r="AN55" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AO55" t="s" s="2">
         <v>483</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>484</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>82</v>
@@ -8609,10 +8610,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8727,10 +8728,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8847,10 +8848,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8969,10 +8970,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8998,13 +8999,13 @@
         <v>243</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>490</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>491</v>
       </c>
       <c r="O59" t="s" s="2">
         <v>257</v>
@@ -9032,14 +9033,14 @@
         <v>82</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="Y59" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="Z59" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="Z59" t="s" s="2">
-        <v>493</v>
-      </c>
       <c r="AA59" t="s" s="2">
         <v>82</v>
       </c>
@@ -9056,7 +9057,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>94</v>
@@ -9077,7 +9078,7 @@
         <v>262</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>264</v>
@@ -9091,10 +9092,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9117,16 +9118,16 @@
         <v>95</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>496</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>497</v>
       </c>
       <c r="M60" t="s" s="2">
         <v>324</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="O60" t="s" s="2">
         <v>326</v>
@@ -9178,7 +9179,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9199,7 +9200,7 @@
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>331</v>
@@ -9213,10 +9214,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9242,13 +9243,13 @@
         <v>243</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>503</v>
       </c>
       <c r="O61" t="s" s="2">
         <v>342</v>
@@ -9300,7 +9301,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9335,10 +9336,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9401,10 +9402,10 @@
         <v>258</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>353</v>
+        <v>504</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>354</v>
+        <v>505</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>82</v>
@@ -9422,7 +9423,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9443,24 +9444,24 @@
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AN62" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="AN62" t="s" s="2">
+      <c r="AO62" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AO62" t="s" s="2">
+      <c r="AP62" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="AP62" t="s" s="2">
-        <v>358</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9486,16 +9487,16 @@
         <v>83</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="N63" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="O63" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
@@ -9544,7 +9545,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9568,10 +9569,10 @@
         <v>82</v>
       </c>
       <c r="AN63" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AO63" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>82</v>

--- a/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
+++ b/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:54:34+00:00</t>
+    <t>2026-05-11T15:54:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
+++ b/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:54:44+00:00</t>
+    <t>2026-05-12T07:59:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
+++ b/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T07:59:38+00:00</t>
+    <t>2026-05-12T09:41:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1028,8 +1028,8 @@
     <t>Observation.value[x]</t>
   </si>
   <si>
-    <t>CodeableConcept
-integer</t>
+    <t xml:space="preserve">integer
+</t>
   </si>
   <si>
     <t>Recorded score value</t>

--- a/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
+++ b/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$62</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2443" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2406" uniqueCount="502">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T09:41:56+00:00</t>
+    <t>2026-05-12T11:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Specialized functional score profile for Glasgow Coma Scale values captured by the registry.</t>
+    <t>Specialized functional score profile for Glasgow Coma Scale component values captured by the registry.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -827,10 +827,19 @@
     <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://snomed.info/sct"/&gt;
+    &lt;code value="386557006"/&gt;
+    &lt;display value="Glasgow coma scale finding (finding)"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>extensible</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/ValueSet/glasgow-coma-scale-vs</t>
+    <t>http://tecnomod-um.org/ValueSet/functional-score-vs</t>
   </si>
   <si>
     <t xml:space="preserve">obs-7
@@ -1026,10 +1035,6 @@
   </si>
   <si>
     <t>Observation.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">integer
-</t>
   </si>
   <si>
     <t>Recorded score value</t>
@@ -1052,13 +1057,6 @@
     <t>An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
   </si>
   <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
-    <t>closed</t>
-  </si>
-  <si>
     <t>obs-7
 obs-6</t>
   </si>
@@ -1075,18 +1073,6 @@
     <t>363714003 |Interprets|</t>
   </si>
   <si>
-    <t>Observation.value[x]:valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>Actual result</t>
-  </si>
-  <si>
-    <t>http://tecnomod-um.org/ValueSet/mrs-score-vs</t>
-  </si>
-  <si>
     <t>Observation.dataAbsentReason</t>
   </si>
   <si>
@@ -1135,7 +1121,10 @@
     <t>For some results, particularly numeric results, an interpretation is necessary to fully understand the significance of a result.</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/ValueSet/gcsscore-vs</t>
+    <t>Codes identifying interpretations of observations.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|5.0.0</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1510,7 +1499,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|5.0.0|ImagingStudy|5.0.0|ImagingSelection|5.0.0|QuestionnaireResponse|5.0.0|Observation|5.0.0|MolecularSequence|5.0.0|GenomicStudy|5.0.0)
+    <t xml:space="preserve">Reference(Observation)
 </t>
   </si>
   <si>
@@ -1617,12 +1606,6 @@
   </si>
   <si>
     <t>Observation.component.interpretation</t>
-  </si>
-  <si>
-    <t>Codes identifying interpretations of observations.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|5.0.0</t>
   </si>
   <si>
     <t>Observation.component.referenceRange</t>
@@ -1950,7 +1933,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP63"/>
+  <dimension ref="A1:AP62"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="40.0234375" customWidth="true" bestFit="true"/>
@@ -1963,7 +1946,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="140.859375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="139.00390625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -4924,7 +4907,7 @@
         <v>82</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>82</v>
+        <v>258</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>82</v>
@@ -4939,11 +4922,11 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
@@ -4970,36 +4953,36 @@
         <v>94</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>215</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5022,19 +5005,19 @@
         <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -5083,7 +5066,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5098,19 +5081,19 @@
         <v>106</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>82</v>
@@ -5118,10 +5101,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5144,16 +5127,16 @@
         <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5203,7 +5186,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5221,16 +5204,16 @@
         <v>82</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>82</v>
@@ -5238,14 +5221,14 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5264,19 +5247,19 @@
         <v>95</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5325,7 +5308,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5340,19 +5323,19 @@
         <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>82</v>
@@ -5360,14 +5343,14 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5386,19 +5369,19 @@
         <v>95</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5447,7 +5430,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5462,19 +5445,19 @@
         <v>106</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>82</v>
@@ -5482,10 +5465,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5508,16 +5491,16 @@
         <v>95</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5567,7 +5550,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5585,16 +5568,16 @@
         <v>82</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>82</v>
@@ -5602,10 +5585,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5628,17 +5611,17 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -5687,7 +5670,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5702,30 +5685,30 @@
         <v>106</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5733,7 +5716,7 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>94</v>
@@ -5748,7 +5731,7 @@
         <v>95</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>322</v>
+        <v>243</v>
       </c>
       <c r="L32" t="s" s="2">
         <v>323</v>
@@ -5797,17 +5780,19 @@
         <v>82</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="AC32" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>328</v>
+        <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5816,7 +5801,7 @@
         <v>94</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>106</v>
@@ -5828,28 +5813,26 @@
         <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AN32" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AO32" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="AN32" t="s" s="2">
+      <c r="AP32" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="AP32" t="s" s="2">
-        <v>333</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="C33" t="s" s="2">
-        <v>335</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
         <v>82</v>
       </c>
@@ -5867,22 +5850,22 @@
         <v>82</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
         <v>243</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="O33" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -5907,11 +5890,13 @@
         <v>82</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="Y33" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>337</v>
+      </c>
       <c r="Z33" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>82</v>
@@ -5929,7 +5914,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5938,7 +5923,7 @@
         <v>94</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>106</v>
@@ -5950,35 +5935,35 @@
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>330</v>
+        <v>82</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>331</v>
+        <v>139</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>333</v>
+        <v>82</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>82</v>
+        <v>342</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>82</v>
@@ -5993,16 +5978,16 @@
         <v>243</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -6027,13 +6012,13 @@
         <v>82</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>82</v>
@@ -6051,16 +6036,16 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>345</v>
+        <v>82</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>106</v>
@@ -6072,28 +6057,28 @@
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>82</v>
+        <v>349</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>139</v>
+        <v>350</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>82</v>
+        <v>352</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>348</v>
+        <v>82</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6112,19 +6097,19 @@
         <v>82</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>243</v>
+        <v>354</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -6149,29 +6134,31 @@
         <v>82</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="Y35" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF35" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="AA35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6192,24 +6179,24 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>354</v>
+        <v>82</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>357</v>
+        <v>82</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6220,7 +6207,7 @@
         <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>82</v>
@@ -6232,20 +6219,18 @@
         <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>359</v>
+        <v>243</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>363</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>82</v>
       </c>
@@ -6269,13 +6254,13 @@
         <v>82</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>82</v>
+        <v>365</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>82</v>
+        <v>366</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>82</v>
+        <v>367</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>82</v>
@@ -6293,16 +6278,16 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>82</v>
+        <v>368</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>106</v>
@@ -6314,24 +6299,24 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>82</v>
+        <v>369</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>82</v>
+        <v>372</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6354,16 +6339,16 @@
         <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>243</v>
+        <v>374</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6389,13 +6374,13 @@
         <v>82</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>370</v>
+        <v>82</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>371</v>
+        <v>82</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>372</v>
+        <v>82</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>82</v>
@@ -6413,7 +6398,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6422,7 +6407,7 @@
         <v>94</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>106</v>
@@ -6434,16 +6419,16 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>374</v>
+        <v>82</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>375</v>
+        <v>82</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>377</v>
+        <v>82</v>
       </c>
     </row>
     <row r="38" hidden="true">
@@ -6474,18 +6459,20 @@
         <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="N38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>82</v>
       </c>
@@ -6509,13 +6496,13 @@
         <v>82</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>82</v>
+        <v>365</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>82</v>
+        <v>383</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>82</v>
+        <v>384</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>82</v>
@@ -6542,7 +6529,7 @@
         <v>94</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>373</v>
+        <v>82</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>106</v>
@@ -6557,10 +6544,10 @@
         <v>82</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>82</v>
+        <v>385</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>82</v>
@@ -6568,10 +6555,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6594,20 +6581,18 @@
         <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>243</v>
+        <v>388</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>387</v>
-      </c>
+        <v>391</v>
+      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>82</v>
       </c>
@@ -6631,13 +6616,13 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>370</v>
+        <v>82</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>388</v>
+        <v>82</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>389</v>
+        <v>82</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -6655,7 +6640,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6667,7 +6652,7 @@
         <v>82</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>106</v>
+        <v>392</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>82</v>
@@ -6676,24 +6661,24 @@
         <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>82</v>
+        <v>393</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>82</v>
+        <v>396</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6716,16 +6701,16 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6775,7 +6760,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6787,7 +6772,7 @@
         <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>397</v>
+        <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>82</v>
@@ -6796,24 +6781,24 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6824,7 +6809,7 @@
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>82</v>
@@ -6836,18 +6821,20 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>403</v>
+        <v>186</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>409</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>410</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
@@ -6895,19 +6882,19 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>106</v>
+        <v>411</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>82</v>
@@ -6916,24 +6903,24 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>407</v>
+        <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>410</v>
+        <v>82</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6944,7 +6931,7 @@
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>82</v>
@@ -6956,20 +6943,16 @@
         <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>412</v>
+        <v>191</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>415</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>82</v>
       </c>
@@ -7017,19 +7000,19 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>411</v>
+        <v>193</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>82</v>
+        <v>194</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>416</v>
+        <v>82</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>82</v>
@@ -7041,10 +7024,10 @@
         <v>82</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>417</v>
+        <v>82</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>418</v>
+        <v>195</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>82</v>
@@ -7052,21 +7035,21 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>82</v>
@@ -7078,15 +7061,17 @@
         <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>190</v>
+        <v>141</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7135,19 +7120,19 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>194</v>
+        <v>82</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>82</v>
+        <v>147</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>82</v>
@@ -7170,14 +7155,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>154</v>
+        <v>201</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7190,24 +7175,26 @@
         <v>82</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
         <v>141</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="N44" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="O44" s="2"/>
+      <c r="O44" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
       </c>
@@ -7255,7 +7242,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7282,7 +7269,7 @@
         <v>82</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>195</v>
+        <v>139</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>82</v>
@@ -7290,46 +7277,42 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>201</v>
+        <v>82</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>141</v>
+        <v>418</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>202</v>
+        <v>419</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>420</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>82</v>
       </c>
@@ -7377,19 +7360,19 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>204</v>
+        <v>417</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>82</v>
+        <v>421</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>147</v>
+        <v>106</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
@@ -7401,10 +7384,10 @@
         <v>82</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>82</v>
+        <v>412</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>139</v>
+        <v>422</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>82</v>
@@ -7412,10 +7395,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7438,7 +7421,7 @@
         <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="L46" t="s" s="2">
         <v>424</v>
@@ -7495,7 +7478,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7504,7 +7487,7 @@
         <v>94</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>106</v>
@@ -7519,10 +7502,10 @@
         <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>82</v>
@@ -7530,10 +7513,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7556,13 +7539,13 @@
         <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>423</v>
+        <v>243</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7589,13 +7572,13 @@
         <v>82</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>82</v>
+        <v>259</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>82</v>
+        <v>430</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>82</v>
+        <v>431</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>82</v>
@@ -7613,7 +7596,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7622,7 +7605,7 @@
         <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>426</v>
+        <v>82</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>106</v>
@@ -7637,10 +7620,10 @@
         <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>82</v>
@@ -7648,10 +7631,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7677,13 +7660,17 @@
         <v>243</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+        <v>435</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>437</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
       </c>
@@ -7707,13 +7694,13 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -7731,7 +7718,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7752,13 +7739,13 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>82</v>
+        <v>440</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>417</v>
+        <v>441</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>437</v>
+        <v>351</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>82</v>
@@ -7766,10 +7753,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7780,7 +7767,7 @@
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>82</v>
@@ -7795,16 +7782,16 @@
         <v>243</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -7829,13 +7816,13 @@
         <v>82</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>248</v>
+        <v>365</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -7853,13 +7840,13 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>82</v>
@@ -7874,13 +7861,13 @@
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>82</v>
@@ -7888,10 +7875,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7902,7 +7889,7 @@
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>82</v>
@@ -7914,19 +7901,17 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>243</v>
+        <v>450</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>450</v>
-      </c>
+        <v>452</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -7951,13 +7936,13 @@
         <v>82</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>370</v>
+        <v>82</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>452</v>
+        <v>82</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>453</v>
+        <v>82</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>82</v>
@@ -7975,13 +7960,13 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>82</v>
@@ -7996,13 +7981,13 @@
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>445</v>
+        <v>82</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>446</v>
+        <v>82</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>356</v>
+        <v>454</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>82</v>
@@ -8010,10 +7995,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8036,18 +8021,16 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N51" s="2"/>
-      <c r="O51" t="s" s="2">
-        <v>458</v>
-      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>82</v>
       </c>
@@ -8095,7 +8078,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8104,7 +8087,7 @@
         <v>94</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>82</v>
+        <v>421</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>106</v>
@@ -8119,7 +8102,7 @@
         <v>82</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>82</v>
+        <v>412</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>459</v>
@@ -8144,7 +8127,7 @@
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>82</v>
@@ -8153,7 +8136,7 @@
         <v>82</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
         <v>461</v>
@@ -8164,7 +8147,9 @@
       <c r="M52" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="N52" s="2"/>
+      <c r="N52" t="s" s="2">
+        <v>464</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8219,10 +8204,10 @@
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>426</v>
+        <v>82</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>106</v>
@@ -8237,21 +8222,21 @@
         <v>82</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>417</v>
+        <v>465</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>464</v>
+        <v>209</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8265,7 +8250,7 @@
         <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>82</v>
@@ -8274,16 +8259,16 @@
         <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8333,7 +8318,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8357,10 +8342,10 @@
         <v>82</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>209</v>
+        <v>471</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>82</v>
@@ -8368,10 +8353,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8394,7 +8379,7 @@
         <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>472</v>
+        <v>186</v>
       </c>
       <c r="L54" t="s" s="2">
         <v>473</v>
@@ -8405,7 +8390,9 @@
       <c r="N54" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="O54" s="2"/>
+      <c r="O54" t="s" s="2">
+        <v>476</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
       </c>
@@ -8453,7 +8440,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8462,7 +8449,7 @@
         <v>81</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>82</v>
+        <v>261</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>106</v>
@@ -8477,10 +8464,10 @@
         <v>82</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>82</v>
@@ -8488,10 +8475,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8502,7 +8489,7 @@
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>82</v>
@@ -8511,23 +8498,19 @@
         <v>82</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>478</v>
+        <v>191</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>481</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>82</v>
       </c>
@@ -8575,19 +8558,19 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>477</v>
+        <v>193</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>260</v>
+        <v>194</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>82</v>
@@ -8599,10 +8582,10 @@
         <v>82</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>482</v>
+        <v>82</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>483</v>
+        <v>195</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>82</v>
@@ -8610,21 +8593,21 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>82</v>
@@ -8636,15 +8619,17 @@
         <v>82</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>190</v>
+        <v>141</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -8693,19 +8678,19 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>194</v>
+        <v>82</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>82</v>
+        <v>147</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>82</v>
@@ -8728,14 +8713,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>154</v>
+        <v>201</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8748,24 +8733,26 @@
         <v>82</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K57" t="s" s="2">
         <v>141</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="O57" s="2"/>
+      <c r="O57" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
       </c>
@@ -8813,7 +8800,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8840,7 +8827,7 @@
         <v>82</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>195</v>
+        <v>139</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>82</v>
@@ -8848,45 +8835,45 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>201</v>
+        <v>82</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="J58" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>141</v>
+        <v>243</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>202</v>
+        <v>483</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>203</v>
+        <v>484</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>157</v>
+        <v>485</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>158</v>
+        <v>257</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -8911,13 +8898,13 @@
         <v>82</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>82</v>
+        <v>365</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>82</v>
+        <v>486</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>82</v>
+        <v>487</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>82</v>
@@ -8935,34 +8922,34 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>204</v>
+        <v>482</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>82</v>
+        <v>261</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>147</v>
+        <v>106</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>82</v>
+        <v>263</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>82</v>
+        <v>488</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>82</v>
+        <v>265</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>139</v>
+        <v>215</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>82</v>
@@ -8970,10 +8957,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8981,7 +8968,7 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>94</v>
@@ -8996,19 +8983,19 @@
         <v>95</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>243</v>
+        <v>490</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>489</v>
+        <v>324</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>257</v>
+        <v>326</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -9033,13 +9020,13 @@
         <v>82</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>370</v>
+        <v>82</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>491</v>
+        <v>82</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>492</v>
+        <v>82</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>82</v>
@@ -9057,16 +9044,16 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>260</v>
+        <v>82</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>106</v>
@@ -9075,19 +9062,19 @@
         <v>82</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>262</v>
+        <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>493</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>264</v>
+        <v>329</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>215</v>
+        <v>330</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>82</v>
+        <v>331</v>
       </c>
     </row>
     <row r="60" hidden="true">
@@ -9115,22 +9102,22 @@
         <v>82</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>496</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>497</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9155,13 +9142,13 @@
         <v>82</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>82</v>
+        <v>259</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>82</v>
+        <v>337</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>82</v>
+        <v>338</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>82</v>
@@ -9200,35 +9187,35 @@
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>498</v>
+        <v>82</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>331</v>
+        <v>139</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>333</v>
+        <v>82</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>82</v>
+        <v>342</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>82</v>
@@ -9243,16 +9230,16 @@
         <v>243</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>500</v>
+        <v>343</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>501</v>
+        <v>344</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>502</v>
+        <v>345</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9277,13 +9264,13 @@
         <v>82</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9301,13 +9288,13 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>82</v>
@@ -9322,28 +9309,28 @@
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>82</v>
+        <v>349</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>139</v>
+        <v>350</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>82</v>
+        <v>352</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>348</v>
+        <v>82</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9362,19 +9349,19 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>243</v>
+        <v>83</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>349</v>
+        <v>500</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>350</v>
+        <v>501</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>351</v>
+        <v>409</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>352</v>
+        <v>410</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>82</v>
@@ -9399,13 +9386,13 @@
         <v>82</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>258</v>
+        <v>82</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>504</v>
+        <v>82</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>505</v>
+        <v>82</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>82</v>
@@ -9423,7 +9410,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9444,142 +9431,20 @@
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>354</v>
+        <v>82</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>355</v>
+        <v>412</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>356</v>
+        <v>413</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="63" hidden="true">
-      <c r="A63" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="C63" s="2"/>
-      <c r="D63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E63" s="2"/>
-      <c r="F63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="P63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q63" s="2"/>
-      <c r="R63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="AG63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="AP63" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP63">
+  <autoFilter ref="A1:AP62">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9589,7 +9454,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI62">
+  <conditionalFormatting sqref="A2:AI61">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
+++ b/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T11:55:23+00:00</t>
+    <t>2026-05-13T14:14:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
+++ b/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:14:43+00:00</t>
+    <t>2026-05-13T15:23:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
+++ b/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T15:23:44+00:00</t>
+    <t>2026-05-14T08:09:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
+++ b/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T08:09:55+00:00</t>
+    <t>2026-05-14T08:55:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
+++ b/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T08:55:50+00:00</t>
+    <t>2026-05-14T09:35:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
+++ b/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T09:35:04+00:00</t>
+    <t>2026-05-14T11:02:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
+++ b/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T11:02:20+00:00</t>
+    <t>2026-05-15T10:10:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
+++ b/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T10:10:20+00:00</t>
+    <t>2026-06-01T07:47:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
+++ b/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T07:47:29+00:00</t>
+    <t>2026-06-01T10:24:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
+++ b/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T10:24:12+00:00</t>
+    <t>2026-06-01T10:42:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
+++ b/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T10:42:50+00:00</t>
+    <t>2026-06-01T12:57:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
+++ b/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T12:57:35+00:00</t>
+    <t>2026-06-02T10:42:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
+++ b/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T10:42:43+00:00</t>
+    <t>2026-06-03T07:55:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
+++ b/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T07:55:03+00:00</t>
+    <t>2026-06-03T14:48:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
+++ b/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T14:48:08+00:00</t>
+    <t>2026-06-03T14:50:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
+++ b/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T14:50:23+00:00</t>
+    <t>2026-06-08T09:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
+++ b/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T09:55:23+00:00</t>
+    <t>2026-06-08T10:51:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
+++ b/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T10:51:55+00:00</t>
+    <t>2026-06-08T11:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
+++ b/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T11:21:15+00:00</t>
+    <t>2026-06-11T11:47:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
+++ b/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T11:47:40+00:00</t>
+    <t>2026-06-11T14:44:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
+++ b/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:44:28+00:00</t>
+    <t>2026-06-12T09:34:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
+++ b/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T09:34:13+00:00</t>
+    <t>2026-07-01T13:43:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
+++ b/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T13:43:23+00:00</t>
+    <t>2026-07-09T09:09:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
+++ b/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T09:09:43+00:00</t>
+    <t>2026-07-13T09:21:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
+++ b/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T09:21:26+00:00</t>
+    <t>2026-07-13T09:30:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
+++ b/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T09:30:27+00:00</t>
+    <t>2026-07-14T07:23:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
+++ b/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-14T07:23:58+00:00</t>
+    <t>2026-07-17T09:40:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
+++ b/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T09:40:30+00:00</t>
+    <t>2026-07-21T08:04:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
+++ b/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/StructureDefinition/glasgow-coma-scale-observation-profile</t>
+    <t>http://qualityregistry.org/StructureDefinition/glasgow-coma-scale-observation-profile</t>
   </si>
   <si>
     <t>Version</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T08:04:16+00:00</t>
+    <t>2026-08-31T09:17:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Tecnomod / Universidad de Murcia (http://tecnomod-um.org)</t>
+    <t>Tecnomod / Universidad de Murcia (http://qualityregistry.org)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -117,7 +117,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/StructureDefinition/functional-score-observation-profile</t>
+    <t>http://qualityregistry.org/StructureDefinition/functional-score-observation-profile</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -485,7 +485,7 @@
     <t>observationTimingContext</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://tecnomod-um.org/StructureDefinition/observation-timing-context-ext}
+    <t xml:space="preserve">Extension {http://qualityregistry.org/StructureDefinition/observation-timing-context-ext}
 </t>
   </si>
   <si>
@@ -839,7 +839,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/ValueSet/functional-score-vs</t>
+    <t>http://qualityregistry.org/ValueSet/functional-score-vs</t>
   </si>
   <si>
     <t xml:space="preserve">obs-7
@@ -864,7 +864,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://tecnomod-um.org/StructureDefinition/resq-patient-profile)
+    <t xml:space="preserve">Reference(http://qualityregistry.org/StructureDefinition/resq-patient-profile)
 </t>
   </si>
   <si>
@@ -918,7 +918,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://tecnomod-um.org/StructureDefinition/stroke-encounter-profile)
+    <t xml:space="preserve">Reference(http://qualityregistry.org/StructureDefinition/stroke-encounter-profile)
 </t>
   </si>
   <si>

--- a/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
+++ b/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T09:17:06+00:00</t>
+    <t>2026-08-31T10:08:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
+++ b/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T10:08:26+00:00</t>
+    <t>2026-09-04T09:44:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
+++ b/StructureDefinition-glasgow-coma-scale-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T09:44:50+00:00</t>
+    <t>2026-09-04T10:11:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
